--- a/exports/trend_1d/CIPLA_full_report.xlsx
+++ b/exports/trend_1d/CIPLA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>655.04</v>
+        <v>629.65</v>
       </c>
       <c r="I2" t="n">
         <v>648.1143695467659</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>2.66</v>
+        <v>-1.31</v>
       </c>
       <c r="L2" t="n">
-        <v>0.85</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="N2" t="n">
-        <v>2.77</v>
+        <v>3.88</v>
       </c>
       <c r="O2" t="n">
         <v>1.05</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>12.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>669.85</v>
+        <v>716.95</v>
       </c>
       <c r="I3" t="n">
         <v>696.3366543854961</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.38</v>
+        <v>-13.86</v>
       </c>
       <c r="L3" t="n">
-        <v>11.47</v>
+        <v>15.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.79</v>
+        <v>2.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>7.03</v>
       </c>
       <c r="O3" t="n">
         <v>-3.88</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.78</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H4" t="n">
-        <v>680.4</v>
+        <v>660</v>
       </c>
       <c r="I4" t="n">
         <v>673.9871871647346</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.1</v>
+        <v>-7.94</v>
       </c>
       <c r="L4" t="n">
-        <v>6.26</v>
+        <v>8.15</v>
       </c>
       <c r="M4" t="n">
         <v>1.31</v>
       </c>
       <c r="N4" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>7.03</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.74</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42188</v>
+        <v>42191</v>
       </c>
       <c r="H5" t="n">
-        <v>631.54</v>
+        <v>653.7</v>
       </c>
       <c r="I5" t="n">
         <v>636.9331778924961</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K5" t="n">
-        <v>4.31</v>
+        <v>0.95</v>
       </c>
       <c r="L5" t="n">
         <v>5.45</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.65</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>697.4</v>
+        <v>635.85</v>
       </c>
       <c r="I6" t="n">
         <v>683.7191176833484</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>6.69</v>
+        <v>-2.73</v>
       </c>
       <c r="L6" t="n">
         <v>4.64</v>
       </c>
       <c r="M6" t="n">
-        <v>1.68</v>
+        <v>3.21</v>
       </c>
       <c r="N6" t="n">
-        <v>4.93</v>
+        <v>8.83</v>
       </c>
       <c r="O6" t="n">
         <v>3.51</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>15.39</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42285</v>
+        <v>42286</v>
       </c>
       <c r="H7" t="n">
-        <v>680.25</v>
+        <v>689.55</v>
       </c>
       <c r="I7" t="n">
         <v>684.2356477112235</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.98</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>8.44</v>
+        <v>8.81</v>
       </c>
       <c r="M7" t="n">
         <v>3.14</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>7.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H8" t="n">
-        <v>658.15</v>
+        <v>647.6</v>
       </c>
       <c r="I8" t="n">
         <v>648.8539628556346</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.55</v>
+        <v>-6.08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.59</v>
+        <v>7.39</v>
       </c>
       <c r="M8" t="n">
-        <v>0.89</v>
+        <v>2.13</v>
       </c>
       <c r="N8" t="n">
         <v>2.16</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.32</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42485</v>
+        <v>42486</v>
       </c>
       <c r="H9" t="n">
-        <v>526.5</v>
+        <v>540.5</v>
       </c>
       <c r="I9" t="n">
         <v>537.5817534100598</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K9" t="n">
-        <v>18.7</v>
+        <v>16.54</v>
       </c>
       <c r="L9" t="n">
         <v>2.13</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42510</v>
+        <v>42513</v>
       </c>
       <c r="H10" t="n">
-        <v>507.1</v>
+        <v>497.4</v>
       </c>
       <c r="I10" t="n">
         <v>506.3601362323568</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.18</v>
+        <v>-7.97</v>
       </c>
       <c r="L10" t="n">
-        <v>7.27</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>0.9399999999999999</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.86</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42549</v>
+        <v>42550</v>
       </c>
       <c r="H11" t="n">
-        <v>497.35</v>
+        <v>502.45</v>
       </c>
       <c r="I11" t="n">
         <v>500.8292333206733</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01</v>
+        <v>-1.02</v>
       </c>
       <c r="L11" t="n">
         <v>2.53</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.12</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42649</v>
+        <v>42650</v>
       </c>
       <c r="H12" t="n">
-        <v>578.8</v>
+        <v>570.05</v>
       </c>
       <c r="I12" t="n">
         <v>574.5877484938892</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
-        <v>15.2</v>
+        <v>13.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.27</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H13" t="n">
-        <v>526.3</v>
+        <v>563.7</v>
       </c>
       <c r="I13" t="n">
         <v>563.6204256732201</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>7.67</v>
+        <v>1.11</v>
       </c>
       <c r="L13" t="n">
         <v>5.34</v>
       </c>
       <c r="M13" t="n">
-        <v>2.81</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>1.86</v>
+        <v>7.11</v>
       </c>
       <c r="O13" t="n">
         <v>-1.51</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.17</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42845</v>
+        <v>42846</v>
       </c>
       <c r="H14" t="n">
-        <v>574.05</v>
+        <v>564.45</v>
       </c>
       <c r="I14" t="n">
         <v>573.6100161952722</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K14" t="n">
-        <v>1.84</v>
+        <v>0.13</v>
       </c>
       <c r="L14" t="n">
         <v>6.23</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.98</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42892</v>
+        <v>42893</v>
       </c>
       <c r="H15" t="n">
-        <v>534.65</v>
+        <v>540.2</v>
       </c>
       <c r="I15" t="n">
         <v>538.0442413736398</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K15" t="n">
-        <v>5.28</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.69</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.99</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H16" t="n">
-        <v>602.45</v>
+        <v>593.65</v>
       </c>
       <c r="I16" t="n">
         <v>596.462681028063</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K16" t="n">
-        <v>11.52</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>11.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43138</v>
+        <v>43139</v>
       </c>
       <c r="H17" t="n">
-        <v>569.25</v>
+        <v>612.65</v>
       </c>
       <c r="I17" t="n">
         <v>610.5381277868237</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" t="n">
-        <v>4.11</v>
+        <v>-3.2</v>
       </c>
       <c r="L17" t="n">
         <v>6.29</v>
       </c>
       <c r="M17" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="N17" t="n">
-        <v>3.53</v>
+        <v>7.62</v>
       </c>
       <c r="O17" t="n">
         <v>-1.46</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>11.78</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43174</v>
+        <v>43175</v>
       </c>
       <c r="H18" t="n">
-        <v>571.15</v>
+        <v>559.4</v>
       </c>
       <c r="I18" t="n">
         <v>566.5885468590649</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.77</v>
+        <v>-8.69</v>
       </c>
       <c r="L18" t="n">
-        <v>8.01</v>
+        <v>9.08</v>
       </c>
       <c r="M18" t="n">
         <v>2.88</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>7.62</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43203</v>
+        <v>43206</v>
       </c>
       <c r="H19" t="n">
-        <v>555.5</v>
+        <v>584.95</v>
       </c>
       <c r="I19" t="n">
         <v>583.9329943099513</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7</v>
+        <v>-4.57</v>
       </c>
       <c r="L19" t="n">
-        <v>3.49</v>
+        <v>5.08</v>
       </c>
       <c r="M19" t="n">
         <v>1.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>10.11</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43235</v>
+        <v>43236</v>
       </c>
       <c r="H20" t="n">
-        <v>575.8</v>
+        <v>559.9</v>
       </c>
       <c r="I20" t="n">
         <v>573.3958903176955</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.56</v>
+        <v>-4.28</v>
       </c>
       <c r="L20" t="n">
-        <v>5.45</v>
+        <v>6.66</v>
       </c>
       <c r="M20" t="n">
         <v>2.22</v>
       </c>
       <c r="N20" t="n">
-        <v>2.13</v>
+        <v>2.76</v>
       </c>
       <c r="O20" t="n">
         <v>5.3</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43263</v>
+        <v>43264</v>
       </c>
       <c r="H21" t="n">
-        <v>567.1</v>
+        <v>582.1</v>
       </c>
       <c r="I21" t="n">
         <v>572.3447075033187</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.29</v>
+        <v>-3.96</v>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.74</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43383</v>
+        <v>43384</v>
       </c>
       <c r="H22" t="n">
-        <v>639.6</v>
+        <v>616.2</v>
       </c>
       <c r="I22" t="n">
         <v>621.7996890259454</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K22" t="n">
-        <v>9.880000000000001</v>
+        <v>5.86</v>
       </c>
       <c r="L22" t="n">
         <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>0.91</v>
+        <v>1.89</v>
       </c>
       <c r="N22" t="n">
-        <v>2.76</v>
+        <v>3.66</v>
       </c>
       <c r="O22" t="n">
         <v>2.65</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.59</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H23" t="n">
-        <v>508</v>
+        <v>534.95</v>
       </c>
       <c r="I23" t="n">
         <v>527.7216531187979</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K23" t="n">
-        <v>17.56</v>
+        <v>13.19</v>
       </c>
       <c r="L23" t="n">
         <v>5.75</v>
@@ -1752,7 +2027,7 @@
         <v>0.91</v>
       </c>
       <c r="N23" t="n">
-        <v>5.21</v>
+        <v>5.31</v>
       </c>
       <c r="O23" t="n">
         <v>-3.66</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43665</v>
+        <v>43668</v>
       </c>
       <c r="H24" t="n">
-        <v>536.7</v>
+        <v>530.95</v>
       </c>
       <c r="I24" t="n">
         <v>531.3281407718724</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K24" t="n">
-        <v>0.33</v>
+        <v>-0.75</v>
       </c>
       <c r="L24" t="n">
         <v>5.77</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43762</v>
+        <v>43763</v>
       </c>
       <c r="H25" t="n">
-        <v>446.85</v>
+        <v>459.85</v>
       </c>
       <c r="I25" t="n">
         <v>456.8634944644588</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K25" t="n">
-        <v>15.84</v>
+        <v>13.39</v>
       </c>
       <c r="L25" t="n">
         <v>1.7</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.64</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H26" t="n">
-        <v>461.55</v>
+        <v>451</v>
       </c>
       <c r="I26" t="n">
         <v>457.9883433253051</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K26" t="n">
-        <v>0.37</v>
+        <v>-1.92</v>
       </c>
       <c r="L26" t="n">
         <v>5.32</v>
@@ -1923,7 +2234,7 @@
         <v>1.51</v>
       </c>
       <c r="N26" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="O26" t="n">
         <v>2.91</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.14</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43893</v>
+        <v>43894</v>
       </c>
       <c r="H27" t="n">
-        <v>425.3</v>
+        <v>447.65</v>
       </c>
       <c r="I27" t="n">
         <v>445.1430629356256</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>5.7</v>
+        <v>0.74</v>
       </c>
       <c r="L27" t="n">
         <v>2.96</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>14.12</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H28" t="n">
-        <v>417.1</v>
+        <v>394.75</v>
       </c>
       <c r="I28" t="n">
         <v>398.9335071199289</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.82</v>
+        <v>-11.82</v>
       </c>
       <c r="L28" t="n">
-        <v>8.369999999999999</v>
+        <v>12.71</v>
       </c>
       <c r="M28" t="n">
         <v>3.54</v>
       </c>
       <c r="N28" t="n">
-        <v>2.12</v>
+        <v>5.36</v>
       </c>
       <c r="O28" t="n">
         <v>5.26</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.75</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H29" t="n">
-        <v>449.2</v>
+        <v>492.25</v>
       </c>
       <c r="I29" t="n">
         <v>456.4075963122872</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K29" t="n">
-        <v>-13.79</v>
+        <v>-24.7</v>
       </c>
       <c r="L29" t="n">
-        <v>15.19</v>
+        <v>30.06</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>6.63</v>
       </c>
       <c r="N29" t="n">
-        <v>8.57</v>
+        <v>9.58</v>
       </c>
       <c r="O29" t="n">
         <v>-5.36</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>21.13</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H30" t="n">
-        <v>763.2</v>
+        <v>717.3</v>
       </c>
       <c r="I30" t="n">
         <v>731.8162294981012</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K30" t="n">
-        <v>55.04</v>
+        <v>45.72</v>
       </c>
       <c r="L30" t="n">
         <v>8.18</v>
@@ -2151,7 +2510,7 @@
         <v>2.94</v>
       </c>
       <c r="N30" t="n">
-        <v>4.73</v>
+        <v>6.01</v>
       </c>
       <c r="O30" t="n">
         <v>9.58</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.85</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44186</v>
+        <v>44187</v>
       </c>
       <c r="H31" t="n">
-        <v>778.5</v>
+        <v>795</v>
       </c>
       <c r="I31" t="n">
         <v>794.5674065280591</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.529999999999999</v>
+        <v>-10.83</v>
       </c>
       <c r="L31" t="n">
         <v>13.89</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.4</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H32" t="n">
-        <v>807.35</v>
+        <v>792.45</v>
       </c>
       <c r="I32" t="n">
         <v>794.114843310782</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K32" t="n">
-        <v>1.55</v>
+        <v>-0.32</v>
       </c>
       <c r="L32" t="n">
         <v>4.26</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>10.25</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44287</v>
+        <v>44291</v>
       </c>
       <c r="H33" t="n">
-        <v>818.3</v>
+        <v>819.75</v>
       </c>
       <c r="I33" t="n">
         <v>818.8551245331867</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.26</v>
+        <v>-3.45</v>
       </c>
       <c r="L33" t="n">
-        <v>3.98</v>
+        <v>4.36</v>
       </c>
       <c r="M33" t="n">
         <v>1.13</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.96</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H34" t="n">
-        <v>950.55</v>
+        <v>913.1</v>
       </c>
       <c r="I34" t="n">
         <v>936.8542851869324</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K34" t="n">
-        <v>15.96</v>
+        <v>11.39</v>
       </c>
       <c r="L34" t="n">
         <v>1.67</v>
@@ -2379,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.49</v>
+        <v>3.94</v>
       </c>
       <c r="O34" t="n">
         <v>0.18</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.17</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H35" t="n">
-        <v>934.7</v>
+        <v>947.8</v>
       </c>
       <c r="I35" t="n">
         <v>947.480976546037</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.37</v>
+        <v>-3.8</v>
       </c>
       <c r="L35" t="n">
         <v>4.97</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>6.67</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44474</v>
+        <v>44475</v>
       </c>
       <c r="H36" t="n">
-        <v>934.55</v>
+        <v>913.45</v>
       </c>
       <c r="I36" t="n">
         <v>923.0984947744967</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.4</v>
+        <v>-3.62</v>
       </c>
       <c r="L36" t="n">
-        <v>2.93</v>
+        <v>3.87</v>
       </c>
       <c r="M36" t="n">
         <v>0.4</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H37" t="n">
-        <v>899.95</v>
+        <v>966.7</v>
       </c>
       <c r="I37" t="n">
         <v>955.0894138709015</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K37" t="n">
-        <v>1.48</v>
+        <v>-5.83</v>
       </c>
       <c r="L37" t="n">
-        <v>3.33</v>
+        <v>6.85</v>
       </c>
       <c r="M37" t="n">
         <v>1.32</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>7.42</v>
       </c>
       <c r="O37" t="n">
         <v>-2.26</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>11.88</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44536</v>
+        <v>44537</v>
       </c>
       <c r="H38" t="n">
-        <v>894.95</v>
+        <v>889.25</v>
       </c>
       <c r="I38" t="n">
         <v>891.0877105033713</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.42</v>
+        <v>-8.01</v>
       </c>
       <c r="L38" t="n">
-        <v>7.87</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>0.88</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>9.58</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44558</v>
+        <v>44559</v>
       </c>
       <c r="H39" t="n">
-        <v>933.3</v>
+        <v>935.55</v>
       </c>
       <c r="I39" t="n">
         <v>935.1485128834468</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.95</v>
+        <v>-5.21</v>
       </c>
       <c r="L39" t="n">
-        <v>5.29</v>
+        <v>6.56</v>
       </c>
       <c r="M39" t="n">
         <v>0.87</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.92</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44580</v>
+        <v>44581</v>
       </c>
       <c r="H40" t="n">
-        <v>895.65</v>
+        <v>882.35</v>
       </c>
       <c r="I40" t="n">
         <v>890.967353186365</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.26</v>
+        <v>-5.69</v>
       </c>
       <c r="L40" t="n">
-        <v>5.39</v>
+        <v>5.93</v>
       </c>
       <c r="M40" t="n">
         <v>0.64</v>
       </c>
       <c r="N40" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O40" t="n">
         <v>0.24</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.62</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44586</v>
+        <v>44588</v>
       </c>
       <c r="H41" t="n">
-        <v>905.65</v>
+        <v>927.6</v>
       </c>
       <c r="I41" t="n">
         <v>922.4332889040946</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.64</v>
+        <v>-5.13</v>
       </c>
       <c r="L41" t="n">
-        <v>3.02</v>
+        <v>5.57</v>
       </c>
       <c r="M41" t="n">
         <v>0.47</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.07</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44609</v>
+        <v>44610</v>
       </c>
       <c r="H42" t="n">
-        <v>928.2</v>
+        <v>909.1</v>
       </c>
       <c r="I42" t="n">
         <v>910.9840644386192</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K42" t="n">
-        <v>0.06</v>
+        <v>-1.99</v>
       </c>
       <c r="L42" t="n">
         <v>4.38</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.57</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44627</v>
+        <v>44628</v>
       </c>
       <c r="H43" t="n">
-        <v>941.15</v>
+        <v>969.55</v>
       </c>
       <c r="I43" t="n">
         <v>966.2538965081869</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.53</v>
+        <v>-6.65</v>
       </c>
       <c r="L43" t="n">
-        <v>4.06</v>
+        <v>7.47</v>
       </c>
       <c r="M43" t="n">
         <v>0.8</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.25</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44672</v>
+        <v>44673</v>
       </c>
       <c r="H44" t="n">
-        <v>998.55</v>
+        <v>967</v>
       </c>
       <c r="I44" t="n">
         <v>975.7082064686919</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K44" t="n">
-        <v>2.99</v>
+        <v>-0.26</v>
       </c>
       <c r="L44" t="n">
         <v>3.52</v>
@@ -2949,7 +3476,7 @@
         <v>0.73</v>
       </c>
       <c r="N44" t="n">
-        <v>2.68</v>
+        <v>3.16</v>
       </c>
       <c r="O44" t="n">
         <v>3.02</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>10.17</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44771</v>
+        <v>44774</v>
       </c>
       <c r="H45" t="n">
-        <v>977.4</v>
+        <v>1004.55</v>
       </c>
       <c r="I45" t="n">
         <v>991.9413158331847</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.08</v>
+        <v>-3.88</v>
       </c>
       <c r="L45" t="n">
-        <v>4.12</v>
+        <v>6.62</v>
       </c>
       <c r="M45" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="N45" t="n">
         <v>4.31</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.86</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44882</v>
+        <v>44883</v>
       </c>
       <c r="H46" t="n">
-        <v>1119.5</v>
+        <v>1102.4</v>
       </c>
       <c r="I46" t="n">
         <v>1108.81383941148</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K46" t="n">
-        <v>11.44</v>
+        <v>9.74</v>
       </c>
       <c r="L46" t="n">
         <v>1.62</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.49</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H47" t="n">
-        <v>907.15</v>
+        <v>917.95</v>
       </c>
       <c r="I47" t="n">
         <v>910.8069326736423</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K47" t="n">
-        <v>17.71</v>
+        <v>16.73</v>
       </c>
       <c r="L47" t="n">
         <v>4.23</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.83</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45194</v>
+        <v>45195</v>
       </c>
       <c r="H48" t="n">
-        <v>1179.35</v>
+        <v>1163.65</v>
       </c>
       <c r="I48" t="n">
         <v>1176.967645006218</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K48" t="n">
-        <v>28.48</v>
+        <v>26.77</v>
       </c>
       <c r="L48" t="n">
         <v>2.36</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.28</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45217</v>
+        <v>45218</v>
       </c>
       <c r="H49" t="n">
-        <v>1210.6</v>
+        <v>1223.3</v>
       </c>
       <c r="I49" t="n">
         <v>1223.188416593805</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.03</v>
+        <v>-5.13</v>
       </c>
       <c r="L49" t="n">
-        <v>4.8</v>
+        <v>5.27</v>
       </c>
       <c r="M49" t="n">
         <v>2.01</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.49</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="H50" t="n">
-        <v>1271.5</v>
+        <v>1170.65</v>
       </c>
       <c r="I50" t="n">
         <v>1209.096295765054</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K50" t="n">
-        <v>3.94</v>
+        <v>-4.3</v>
       </c>
       <c r="L50" t="n">
         <v>7.46</v>
@@ -3291,7 +3890,7 @@
         <v>0.63</v>
       </c>
       <c r="N50" t="n">
-        <v>2.23</v>
+        <v>7.93</v>
       </c>
       <c r="O50" t="n">
         <v>1.05</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>11.31</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45292</v>
+        <v>45293</v>
       </c>
       <c r="H51" t="n">
-        <v>1251</v>
+        <v>1281.55</v>
       </c>
       <c r="I51" t="n">
         <v>1273.940048977538</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.86</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>8.49</v>
+        <v>9.77</v>
       </c>
       <c r="M51" t="n">
         <v>1.66</v>
       </c>
       <c r="N51" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="O51" t="n">
         <v>-7.93</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.27</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45392</v>
+        <v>45394</v>
       </c>
       <c r="H52" t="n">
-        <v>1422.95</v>
+        <v>1396.8</v>
       </c>
       <c r="I52" t="n">
         <v>1412.987698664685</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K52" t="n">
-        <v>11.03</v>
+        <v>8.99</v>
       </c>
       <c r="L52" t="n">
         <v>2.3</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>7.94</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45430</v>
+        <v>45433</v>
       </c>
       <c r="H53" t="n">
-        <v>1404.05</v>
+        <v>1442.3</v>
       </c>
       <c r="I53" t="n">
         <v>1440.805803177298</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.52</v>
+        <v>-3.26</v>
       </c>
       <c r="L53" t="n">
-        <v>2.66</v>
+        <v>3.52</v>
       </c>
       <c r="M53" t="n">
         <v>2.77</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H54" t="n">
-        <v>1598.45</v>
+        <v>1571.75</v>
       </c>
       <c r="I54" t="n">
         <v>1586.519307415452</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K54" t="n">
-        <v>10.83</v>
+        <v>8.98</v>
       </c>
       <c r="L54" t="n">
         <v>3.18</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>9.07</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45595</v>
+        <v>45596</v>
       </c>
       <c r="H55" t="n">
-        <v>1418.25</v>
+        <v>1551.75</v>
       </c>
       <c r="I55" t="n">
         <v>1548.185684532051</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
-        <v>9.77</v>
+        <v>1.27</v>
       </c>
       <c r="L55" t="n">
         <v>2.11</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="N55" t="n">
-        <v>0.96</v>
+        <v>9.41</v>
       </c>
       <c r="O55" t="n">
         <v>-1.67</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>10.83</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="H56" t="n">
-        <v>1469</v>
+        <v>1455.2</v>
       </c>
       <c r="I56" t="n">
         <v>1459.378589140669</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.33</v>
+        <v>-6.22</v>
       </c>
       <c r="L56" t="n">
-        <v>6.31</v>
+        <v>6.41</v>
       </c>
       <c r="M56" t="n">
         <v>0.57</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="H57" t="n">
-        <v>1529.1</v>
+        <v>1537.9</v>
       </c>
       <c r="I57" t="n">
         <v>1532.605559893791</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.08</v>
+        <v>-5.68</v>
       </c>
       <c r="L57" t="n">
         <v>6.37</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.96</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H58" t="n">
-        <v>1468.8</v>
+        <v>1439.2</v>
       </c>
       <c r="I58" t="n">
         <v>1446.263080633761</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.49</v>
+        <v>-6.42</v>
       </c>
       <c r="L58" t="n">
-        <v>4.73</v>
+        <v>6.6</v>
       </c>
       <c r="M58" t="n">
         <v>0.74</v>
       </c>
       <c r="N58" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="O58" t="n">
         <v>0.58</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.77</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45729</v>
+        <v>45733</v>
       </c>
       <c r="H59" t="n">
-        <v>1461.9</v>
+        <v>1492.6</v>
       </c>
       <c r="I59" t="n">
         <v>1483.9897538892</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.58</v>
+        <v>-3.71</v>
       </c>
       <c r="L59" t="n">
         <v>4.36</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.15</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
       <c r="H60" t="n">
-        <v>1482.9</v>
+        <v>1442.2</v>
       </c>
       <c r="I60" t="n">
         <v>1447.364510243934</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.65</v>
+        <v>-3.38</v>
       </c>
       <c r="L60" t="n">
-        <v>2.47</v>
+        <v>3.9</v>
       </c>
       <c r="M60" t="n">
         <v>0.78</v>
       </c>
       <c r="N60" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="O60" t="n">
         <v>2.1</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.15</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H61" t="n">
-        <v>1496.4</v>
+        <v>1515.2</v>
       </c>
       <c r="I61" t="n">
         <v>1505.5101177563</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.76</v>
+        <v>-5.06</v>
       </c>
       <c r="L61" t="n">
         <v>5.62</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.44</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H62" t="n">
-        <v>1538</v>
+        <v>1509.7</v>
       </c>
       <c r="I62" t="n">
         <v>1517.126386918036</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K62" t="n">
-        <v>1.5</v>
+        <v>-0.36</v>
       </c>
       <c r="L62" t="n">
         <v>4.22</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>6</v>
+      </c>
+      <c r="U62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>6.42</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="H63" t="n">
-        <v>1569.4</v>
+        <v>1577.6</v>
       </c>
       <c r="I63" t="n">
         <v>1573.727199008525</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.95</v>
+        <v>-4.5</v>
       </c>
       <c r="L63" t="n">
-        <v>4.13</v>
+        <v>4.8</v>
       </c>
       <c r="M63" t="n">
         <v>1.03</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.4</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="H64" t="n">
-        <v>1581.1</v>
+        <v>1540.1</v>
       </c>
       <c r="I64" t="n">
         <v>1564.827914472529</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K64" t="n">
-        <v>0.22</v>
+        <v>-2.38</v>
       </c>
       <c r="L64" t="n">
-        <v>1.22</v>
+        <v>4.67</v>
       </c>
       <c r="M64" t="n">
         <v>1.22</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.7</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H65" t="n">
-        <v>1236.3</v>
+        <v>1305.9</v>
       </c>
       <c r="I65" t="n">
         <v>1274.200658974339</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K65" t="n">
-        <v>19.73</v>
+        <v>15.21</v>
       </c>
       <c r="L65" t="n">
         <v>3.45</v>
@@ -4146,7 +4925,7 @@
         <v>4.07</v>
       </c>
       <c r="N65" t="n">
-        <v>2.05</v>
+        <v>5.63</v>
       </c>
       <c r="O65" t="n">
         <v>-2.59</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>6</v>
+      </c>
+      <c r="U65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.44</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="H66" t="n">
-        <v>1394.7</v>
+        <v>1385</v>
       </c>
       <c r="I66" t="n">
         <v>1391.446535089454</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K66" t="n">
-        <v>6.8</v>
+        <v>6.06</v>
       </c>
       <c r="L66" t="n">
         <v>6</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>6</v>
+      </c>
+      <c r="U66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>36</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9221,7 +10032,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.8</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -9231,7 +10042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -9241,7 +10052,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
@@ -9251,7 +10062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9261,7 +10072,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -9271,7 +10082,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -9281,7 +10092,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -9291,7 +10102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -9301,7 +10112,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.4</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="14">
@@ -9311,7 +10122,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.95</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="15">
@@ -9321,7 +10132,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.36</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="16">
@@ -9331,7 +10142,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="17">
@@ -9341,7 +10152,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55.04</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="18">
@@ -9351,7 +10162,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.8</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="19">
@@ -9361,7 +10172,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.83</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="20">
@@ -9371,7 +10182,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.36</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="21">
@@ -9381,7 +10192,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.19</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="22">
@@ -9391,7 +10202,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -9401,7 +10212,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -9411,7 +10222,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="25">
@@ -9421,7 +10232,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.07</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9431,7 +10242,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.41</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="27">
@@ -9441,7 +10252,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.57</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="28">
@@ -9451,7 +10262,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
